--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run3/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,688 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9426,0.0092,0.0181,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9951,0.0000,0.0000,0.0033</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9826,0.0049,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.0060,0.0000,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.2388,0.0004,0.0009,0.9054</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9623,0.0005,0.0394,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.2782,0.0027,0.7660,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9964,0.0013</t>
+  </si>
+  <si>
+    <t>0.3207,0.0013,0.6902,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9926,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.3751,0.0005,0.7221,0.0001</t>
+  </si>
+  <si>
+    <t>0.0393,0.0006,0.9671,0.0002</t>
+  </si>
+  <si>
+    <t>0.0401,0.0004,0.9634,0.0005</t>
+  </si>
+  <si>
+    <t>0.0045,0.0005,0.9927,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9989,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.2538,0.7639,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9631,0.0116,0.0106,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9958,0.0004,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.1425,0.8565,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0062,0.9970,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0005,0.9692,0.0562</t>
+  </si>
+  <si>
+    <t>0.0007,0.0021,0.9972,0.0003</t>
+  </si>
+  <si>
+    <t>0.0114,0.0000,0.9856,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0327,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9990,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0012,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.0049,0.0003,0.9953</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0182,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0011,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9999,0.0057</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9728,0.9912,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0007,0.9957,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9948,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0012</t>
+  </si>
+  <si>
+    <t>0.0014,0.9980,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.8810,0.0004,0.1998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9904,0.0037,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9996,0.0015</t>
+  </si>
+  <si>
+    <t>0.0000,0.9527,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8772,0.9953,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9811,0.9716,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.1197,0.9962</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0011,0.9993</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0022,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.2248,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9912,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9796,0.8759,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9155,0.9686,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9766,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9657,0.4977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0012,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.1058,0.0006,0.9173,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0000,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0159,0.0003,0.9881,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9976,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.9975,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6737,0.4597,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.7585,0.0092,0.1771,0.0006</t>
+  </si>
+  <si>
+    <t>0.7243,0.0033,0.2030,0.0007</t>
+  </si>
+  <si>
+    <t>0.8122,0.0199,0.0818,0.0007</t>
+  </si>
+  <si>
+    <t>0.0067,0.0032,0.9892,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.9870,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9976,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.4707,0.4149,0.0162,0.0015</t>
+  </si>
+  <si>
+    <t>0.8206,0.2055,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9478,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7583,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0181,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5522,0.0013,0.4126,0.0024</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.9712,0.0142,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0082,0.0001,0.0000,0.9985</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9863,0.9825,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9876,0.0015,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0002,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.4815,0.0030,0.5125,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0002,0.9958,0.0005</t>
-  </si>
-  <si>
-    <t>0.9138,0.0017,0.0819,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.9922,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1390,0.0003,0.8967,0.0005</t>
-  </si>
-  <si>
-    <t>0.7756,0.0008,0.3073,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0006,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.9974,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.0000,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0579,0.9384,0.0016,0.0019</t>
-  </si>
-  <si>
-    <t>0.6706,0.0271,0.1520,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9890,0.1115,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9202,0.0011,0.0824,0.0004</t>
-  </si>
-  <si>
-    <t>0.1989,0.8549,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9990,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9609,0.0662,0.0237</t>
-  </si>
-  <si>
-    <t>0.0039,0.0011,0.9767,0.0091</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9986,0.0007</t>
-  </si>
-  <si>
-    <t>0.0038,0.0001,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.0202,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0027,0.9906,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0202,0.0000,0.9991</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.1505,0.9988,0.0000</t>
+    <t>0.0049,0.9917,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.2480,0.7223,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9912,0.0001,0.0002,0.0069</t>
+  </si>
+  <si>
+    <t>0.0014,0.0508,0.9955,0.0005</t>
+  </si>
+  <si>
+    <t>0.9818,0.0002,0.0032,0.0079</t>
+  </si>
+  <si>
+    <t>0.9964,0.0000,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.0244,0.9740,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0009,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0948,0.5797,0.0709,0.0017</t>
+  </si>
+  <si>
+    <t>0.9404,0.0078,0.0207,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9587,0.0206,0.0077,0.0016</t>
+  </si>
+  <si>
+    <t>0.1620,0.8494,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.0820,0.0143,0.9459,0.0007</t>
+  </si>
+  <si>
+    <t>0.9825,0.0195,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9682,0.0130,0.0052,0.0067</t>
+  </si>
+  <si>
+    <t>0.0000,0.0117,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9893,0.0020,0.0033,0.0027</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0060,0.9942,0.0003</t>
+  </si>
+  <si>
+    <t>0.0205,0.0035,0.9821,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.0015,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0056,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0136,0.0007,0.9901,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.0027,0.9893,0.0003</t>
+  </si>
+  <si>
+    <t>0.1704,0.0147,0.7148,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.5871,0.6341,0.0006</t>
+  </si>
+  <si>
+    <t>0.0430,0.0053,0.9537,0.0001</t>
+  </si>
+  <si>
+    <t>0.5951,0.0034,0.2734,0.0025</t>
+  </si>
+  <si>
+    <t>0.2776,0.0055,0.6689,0.0018</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9988,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.5587,0.4589,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.1659,0.8975,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0468,0.9557,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9850,0.0009,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0002,0.0045,0.0000</t>
+  </si>
+  <si>
+    <t>0.8713,0.0007,0.0164,0.0204</t>
+  </si>
+  <si>
+    <t>0.7907,0.0056,0.1910,0.0001</t>
+  </si>
+  <si>
+    <t>0.1175,0.0034,0.8489,0.0023</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9940,0.0015,0.0012,0.0014</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0033</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0007,0.0003</t>
+    <t>0.0065,0.0067,0.9837,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0008,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.0003,0.9937,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.0012,0.9936,0.0012</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0001,0.0002</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9962,0.0013,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9753,0.9559,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0003</t>
-  </si>
-  <si>
-    <t>0.0030,0.9964,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0456,0.0015,0.9656,0.0014</t>
-  </si>
-  <si>
-    <t>0.4804,0.0018,0.5265,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.9994,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9582,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9910,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0001,0.1804,0.8999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0063,0.9993</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0061,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9217,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9892,0.4453,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.8123,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9925,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9476,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0018,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0006,0.9978,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0000,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.9871,0.0037,0.0011</t>
-  </si>
-  <si>
-    <t>0.0015,0.9958,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1162,0.9155,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.1543,0.0482,0.5566,0.0086</t>
-  </si>
-  <si>
-    <t>0.3342,0.0050,0.5397,0.0012</t>
-  </si>
-  <si>
-    <t>0.1683,0.0462,0.5824,0.0017</t>
-  </si>
-  <si>
-    <t>0.0040,0.0190,0.9771,0.0017</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9933,0.9910,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0816,0.9048,0.0109,0.0004</t>
-  </si>
-  <si>
-    <t>0.5247,0.4446,0.0120,0.0008</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9816,0.9398,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9263,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0028,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.4620,0.0015,0.4468,0.0077</t>
-  </si>
-  <si>
-    <t>0.0197,0.0002,0.9861,0.0002</t>
-  </si>
-  <si>
-    <t>0.8928,0.0063,0.0390,0.0036</t>
-  </si>
-  <si>
-    <t>0.0437,0.0000,0.0000,0.9952</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9913,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0797,0.9175,0.0015,0.0012</t>
+    <t>0.9974,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0032,0.0008,0.0005</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0084,0.9840,0.0044,0.0007</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.2145,0.0002,0.0003,0.9411</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0664,0.9969,0.0004</t>
-  </si>
-  <si>
-    <t>0.9439,0.0000,0.0052,0.0179</t>
-  </si>
-  <si>
-    <t>0.9933,0.0000,0.0003,0.0063</t>
-  </si>
-  <si>
-    <t>0.8718,0.0865,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0005,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0529,0.9264,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.9510,0.0173,0.0101,0.0004</t>
-  </si>
-  <si>
-    <t>0.9913,0.0017,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9861,0.0118,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9466,0.0203,0.0108,0.0008</t>
-  </si>
-  <si>
-    <t>0.0458,0.9439,0.0075,0.0006</t>
-  </si>
-  <si>
-    <t>0.1065,0.0573,0.8971,0.0020</t>
-  </si>
-  <si>
-    <t>0.9897,0.0218,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0018,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9404,0.0582,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.0121,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9654,0.0029,0.0195,0.0039</t>
+    <t>0.0010,0.0015,0.9984,0.0016</t>
+  </si>
+  <si>
+    <t>0.0813,0.2549,0.3966,0.0012</t>
+  </si>
+  <si>
+    <t>0.8913,0.0017,0.0623,0.0080</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.4027,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9994,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0103,0.0408,0.9835,0.0002</t>
-  </si>
-  <si>
-    <t>0.1152,0.0011,0.9303,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0021,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0023,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0027,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.0173,0.0018,0.9809,0.0003</t>
-  </si>
-  <si>
-    <t>0.1318,0.0046,0.8015,0.0008</t>
-  </si>
-  <si>
-    <t>0.5550,0.0138,0.3250,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.5556,0.5838,0.0009</t>
-  </si>
-  <si>
-    <t>0.0025,0.0010,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.9256,0.0240,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.0044,0.0028,0.9899,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.9970,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.2859,0.7167,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.9404,0.0988,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7886,0.3404,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9749,0.0021,0.0088,0.0001</t>
-  </si>
-  <si>
-    <t>0.9808,0.0006,0.0159,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0003,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8444,0.0029,0.1550,0.0001</t>
-  </si>
-  <si>
-    <t>0.1513,0.0002,0.8790,0.0005</t>
-  </si>
-  <si>
-    <t>0.0310,0.0005,0.9722,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.0134,0.9956,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0076,0.0012,0.9885,0.0003</t>
-  </si>
-  <si>
-    <t>0.0050,0.0114,0.9589,0.0028</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
+    <t>0.0002,0.0006,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0113,0.0006,0.9843,0.0013</t>
+  </si>
+  <si>
+    <t>0.9729,0.0009,0.0206,0.0001</t>
+  </si>
+  <si>
+    <t>0.9879,0.0001,0.0122,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0026,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0042,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9991,0.0004,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9958,0.0030,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0015,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9951,0.0029,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9972,0.0012,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0032,0.1361,0.9603,0.0003</t>
-  </si>
-  <si>
-    <t>0.9751,0.0011,0.0120,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0453,0.9870,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0008,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.1863,0.0005,0.7762,0.0059</t>
-  </si>
-  <si>
-    <t>0.9831,0.0028,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.8319,0.0002,0.2211,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0003,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0026,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0055,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0217,0.9928,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.0070,0.9924,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.2729,0.0005,0.6963,0.0086</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0002,0.9912,0.0009</t>
-  </si>
-  <si>
-    <t>0.9787,0.0001,0.0010,0.0185</t>
-  </si>
-  <si>
-    <t>0.0009,0.0044,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.3339,0.0004,0.0000,0.8422</t>
-  </si>
-  <si>
-    <t>0.6569,0.0007,0.0002,0.5044</t>
+    <t>0.0096,0.0056,0.9757,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0069,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0028,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.0119,0.0000,0.9916,0.0002</t>
+  </si>
+  <si>
+    <t>0.7765,0.0002,0.1357,0.0093</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.9970,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0004,0.9971,0.0004</t>
+  </si>
+  <si>
+    <t>0.9509,0.0003,0.0008,0.0592</t>
+  </si>
+  <si>
+    <t>0.0017,0.0064,0.0001,0.9988</t>
+  </si>
+  <si>
+    <t>0.0162,0.0001,0.0001,0.9959</t>
+  </si>
+  <si>
+    <t>0.9738,0.0011,0.0003,0.0144</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1976,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2018,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,7 +2071,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,10 +2096,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2183,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,10 +2194,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2284,7 +2281,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2354,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2368,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2382,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,10 +2390,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2494,7 +2491,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>284</v>
+        <v>327</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,10 +2824,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3012,7 +3009,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,10 +3034,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3208,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3250,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>280</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>284</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3457,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3471,10 +3468,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,10 +3482,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3499,10 +3496,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3513,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3530,7 +3527,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,10 +3608,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3628,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3751,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3765,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3824,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>271</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,10 +4000,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>357</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>271</v>
+        <v>413</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>415</v>
+        <v>270</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4300,7 +4297,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4314,7 +4311,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4328,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,7 +4563,7 @@
         <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4580,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4594,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4605,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,10 +4644,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,10 +4658,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,7 +4745,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>397</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5056,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>431</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5112,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>478</v>
+        <v>394</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5238,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5266,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5277,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,10 +5316,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>393</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>393</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,10 +5428,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
